--- a/outputs/evaluation/architecture/design/v4/CF_M08/run_1/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v4/CF_M08/run_1/CF_M08_arch_eval.xlsx
@@ -508,6 +508,8 @@
         <v>0.8336</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -589,10 +591,8 @@
           <t>fixedType</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1235,14 +1235,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -1261,14 +1258,11 @@
       <c r="P2" t="n">
         <v>66</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1289,7 +1283,6 @@
       <c r="D3" t="n">
         <v>0.8336</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1310,7 +1303,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_22</t>
@@ -1321,7 +1313,6 @@
           <t>system service, data service</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1340,7 +1331,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1391,14 +1381,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -1417,14 +1404,11 @@
       <c r="P4" t="n">
         <v>67</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1470,13 +1454,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Authentication</t>
@@ -1500,13 +1482,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1552,13 +1532,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Email</t>
@@ -1582,13 +1560,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1634,13 +1610,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Analytics</t>
@@ -1664,13 +1638,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1716,13 +1688,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Error monitoring</t>
@@ -1746,13 +1716,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1798,13 +1766,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Payment processing</t>
@@ -1828,13 +1794,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1880,13 +1844,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Cloud storage</t>
@@ -1910,13 +1872,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1957,14 +1917,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -1983,14 +1940,11 @@
       <c r="P11" t="n">
         <v>66</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2031,14 +1985,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -2062,13 +2013,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2114,13 +2063,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>React</t>
@@ -2144,13 +2091,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M08_AU06</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2196,13 +2141,11 @@
           <t>['AU_19']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Brevo</t>
@@ -2226,13 +2169,11 @@
           <t>CF_M08_AU20</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M08_AU21</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2273,14 +2214,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -2304,13 +2242,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2356,13 +2292,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Sentry</t>
@@ -2386,13 +2320,11 @@
           <t>CF_M08_AU18</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M08_AU19</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2438,13 +2370,11 @@
           <t>['AU_06']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
@@ -2468,13 +2398,11 @@
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M08_AU08</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2520,13 +2448,11 @@
           <t>['AU_09']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Google</t>
@@ -2550,13 +2476,11 @@
           <t>CF_M08_AU10</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M08_AU11</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2602,13 +2526,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2632,13 +2554,11 @@
           <t>CF_M08_AU12</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M08_AU13</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2684,13 +2604,11 @@
           <t>['AU_13']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Stripe</t>
@@ -2714,13 +2632,11 @@
           <t>CF_M08_AU14</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M08_AU15</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2766,13 +2682,11 @@
           <t>['AU_21']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_30</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>HTTPS</t>
@@ -2791,14 +2705,11 @@
       <c r="P21" t="n">
         <v>43</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M08_AU23</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2839,14 +2750,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -2865,14 +2773,11 @@
       <c r="P22" t="n">
         <v>41</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2918,13 +2823,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Traefik</t>
@@ -2948,13 +2851,11 @@
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2995,14 +2896,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -3026,13 +2924,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3078,13 +2974,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Next.js</t>
@@ -3108,13 +3002,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M08_AU05</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3160,13 +3052,11 @@
           <t>['AU_15']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Google Analytics</t>
@@ -3190,13 +3080,11 @@
           <t>CF_M08_AU16</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M08_AU17</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3242,13 +3130,11 @@
           <t>['AU_03', 'AU_22']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -3272,13 +3158,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3347,7 +3231,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>security service, system service</t>
@@ -3383,7 +3266,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>system service, authentication service</t>
@@ -3419,7 +3301,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>system service, cloud storage service</t>
@@ -3455,7 +3336,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>system service, payment processing service</t>
@@ -3491,7 +3371,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>system service, analytics service</t>
@@ -3527,7 +3406,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>system service, error monitoring service</t>
@@ -3563,7 +3441,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>system service, email service</t>
@@ -3604,7 +3481,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Security Service (Traefik) manages the routing of HTTP and HTTPS requests to the application Next.js (System Service).</t>
@@ -3696,7 +3572,6 @@
           <t>Amazon EC2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>These services run on Amazon EC2 instances</t>
@@ -3727,7 +3602,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
@@ -3768,7 +3642,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Each of these services is contained in a Docker container</t>
@@ -3804,7 +3677,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
@@ -3815,7 +3687,6 @@
           <t>AU_22</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.676</v>
       </c>
@@ -3836,7 +3707,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
